--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R418"/>
+  <dimension ref="A1:R420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25515,6 +25515,126 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>359.77</v>
+      </c>
+      <c r="C419" t="n">
+        <v>362.51</v>
+      </c>
+      <c r="D419" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="E419" t="n">
+        <v>369.93</v>
+      </c>
+      <c r="F419" t="n">
+        <v>373.77</v>
+      </c>
+      <c r="G419" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="H419" t="n">
+        <v>373.33</v>
+      </c>
+      <c r="I419" t="n">
+        <v>375.52</v>
+      </c>
+      <c r="J419" t="n">
+        <v>375.53</v>
+      </c>
+      <c r="K419" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="L419" t="n">
+        <v>370.71</v>
+      </c>
+      <c r="M419" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="N419" t="n">
+        <v>359.61</v>
+      </c>
+      <c r="O419" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="P419" t="n">
+        <v>362.65</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>360.41</v>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>362.84</v>
+      </c>
+      <c r="C420" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="D420" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="E420" t="n">
+        <v>370.92</v>
+      </c>
+      <c r="F420" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="G420" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="H420" t="n">
+        <v>373.62</v>
+      </c>
+      <c r="I420" t="n">
+        <v>375.61</v>
+      </c>
+      <c r="J420" t="n">
+        <v>376.17</v>
+      </c>
+      <c r="K420" t="n">
+        <v>375.85</v>
+      </c>
+      <c r="L420" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="M420" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="N420" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="O420" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="P420" t="n">
+        <v>363.16</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>360.61</v>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25526,7 +25646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B444"/>
+  <dimension ref="A1:B446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29969,6 +30089,26 @@
       </c>
       <c r="B444" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>-0.85</v>
       </c>
     </row>
   </sheetData>
@@ -30137,28 +30277,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3285063541199019</v>
+        <v>0.325349342329661</v>
       </c>
       <c r="J2" t="n">
+        <v>419</v>
+      </c>
+      <c r="K2" t="n">
         <v>417</v>
       </c>
-      <c r="K2" t="n">
-        <v>415</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1594630381523264</v>
+        <v>0.1581102291364387</v>
       </c>
       <c r="M2" t="n">
-        <v>4.318420110883331</v>
+        <v>4.314689932090038</v>
       </c>
       <c r="N2" t="n">
-        <v>31.63049088347665</v>
+        <v>31.53995095511464</v>
       </c>
       <c r="O2" t="n">
-        <v>5.6240991175011</v>
+        <v>5.616044066343732</v>
       </c>
       <c r="P2" t="n">
-        <v>355.7555282303235</v>
+        <v>355.78875298422</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30215,28 +30355,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5058750779665609</v>
+        <v>0.4995437531678678</v>
       </c>
       <c r="J3" t="n">
+        <v>419</v>
+      </c>
+      <c r="K3" t="n">
         <v>417</v>
       </c>
-      <c r="K3" t="n">
-        <v>415</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.3187863647358236</v>
+        <v>0.3142728809026293</v>
       </c>
       <c r="M3" t="n">
-        <v>4.313857491587737</v>
+        <v>4.327507313666987</v>
       </c>
       <c r="N3" t="n">
-        <v>30.4082736738104</v>
+        <v>30.46894143723305</v>
       </c>
       <c r="O3" t="n">
-        <v>5.51436974402428</v>
+        <v>5.519867882226263</v>
       </c>
       <c r="P3" t="n">
-        <v>356.5877344192484</v>
+        <v>356.6543750872869</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30293,28 +30433,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3291469438969761</v>
+        <v>0.3251456629799145</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K4" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2172343088308251</v>
+        <v>0.2143288884847407</v>
       </c>
       <c r="M4" t="n">
-        <v>3.516136213811222</v>
+        <v>3.517129812127255</v>
       </c>
       <c r="N4" t="n">
-        <v>21.6664847440099</v>
+        <v>21.64588437986004</v>
       </c>
       <c r="O4" t="n">
-        <v>4.654727139587228</v>
+        <v>4.652513769980702</v>
       </c>
       <c r="P4" t="n">
-        <v>368.3347228920603</v>
+        <v>368.3768555057576</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30371,28 +30511,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4015779858666922</v>
+        <v>0.3937257967489245</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K5" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2561750172502321</v>
+        <v>0.2485863528050958</v>
       </c>
       <c r="M5" t="n">
-        <v>3.754053004903202</v>
+        <v>3.767243464430002</v>
       </c>
       <c r="N5" t="n">
-        <v>25.98838049770012</v>
+        <v>26.17272049906289</v>
       </c>
       <c r="O5" t="n">
-        <v>5.097880000323676</v>
+        <v>5.115928117073469</v>
       </c>
       <c r="P5" t="n">
-        <v>367.7403087526396</v>
+        <v>367.82299572264</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30449,28 +30589,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4006119710734198</v>
+        <v>0.3965448448119375</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3320035634522636</v>
+        <v>0.3289252129633994</v>
       </c>
       <c r="M6" t="n">
-        <v>3.203252658742602</v>
+        <v>3.205527233180833</v>
       </c>
       <c r="N6" t="n">
-        <v>17.92192607866545</v>
+        <v>17.91916236706248</v>
       </c>
       <c r="O6" t="n">
-        <v>4.233429588249396</v>
+        <v>4.233103160455989</v>
       </c>
       <c r="P6" t="n">
-        <v>367.5363210127821</v>
+        <v>367.5791493363543</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30527,28 +30667,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4478951828157176</v>
+        <v>0.4444067609439727</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K7" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3694685956401365</v>
+        <v>0.3676664563306185</v>
       </c>
       <c r="M7" t="n">
-        <v>3.136288317624872</v>
+        <v>3.136965099100494</v>
       </c>
       <c r="N7" t="n">
-        <v>19.00147921312172</v>
+        <v>18.97198866755483</v>
       </c>
       <c r="O7" t="n">
-        <v>4.35906861762025</v>
+        <v>4.355684638211866</v>
       </c>
       <c r="P7" t="n">
-        <v>366.3131274179272</v>
+        <v>366.3498612307386</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30605,28 +30745,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3951312382081765</v>
+        <v>0.3932789722815787</v>
       </c>
       <c r="J8" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K8" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3390811145985355</v>
+        <v>0.3392417568218102</v>
       </c>
       <c r="M8" t="n">
-        <v>3.263721819692975</v>
+        <v>3.256667681362513</v>
       </c>
       <c r="N8" t="n">
-        <v>16.89011964997331</v>
+        <v>16.82651082222305</v>
       </c>
       <c r="O8" t="n">
-        <v>4.109759074443819</v>
+        <v>4.102013020728121</v>
       </c>
       <c r="P8" t="n">
-        <v>364.7935672787204</v>
+        <v>364.8130723393589</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30683,28 +30823,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3346371247407345</v>
+        <v>0.3349558468425779</v>
       </c>
       <c r="J9" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K9" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L9" t="n">
-        <v>0.220326863253707</v>
+        <v>0.2225712293626437</v>
       </c>
       <c r="M9" t="n">
-        <v>3.67356649831877</v>
+        <v>3.657658819240203</v>
       </c>
       <c r="N9" t="n">
-        <v>21.99372523964593</v>
+        <v>21.88900601276285</v>
       </c>
       <c r="O9" t="n">
-        <v>4.689746820420686</v>
+        <v>4.67856879961841</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2724028973601</v>
+        <v>366.2690463411745</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30761,28 +30901,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2811954742458633</v>
+        <v>0.2816725820371285</v>
       </c>
       <c r="J10" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K10" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L10" t="n">
-        <v>0.203366357586332</v>
+        <v>0.2057146676989033</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32463639174486</v>
+        <v>3.31108431958543</v>
       </c>
       <c r="N10" t="n">
-        <v>17.19101904881381</v>
+        <v>17.11038431638048</v>
       </c>
       <c r="O10" t="n">
-        <v>4.146205379478181</v>
+        <v>4.136470030881462</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8223091768928</v>
+        <v>367.8172834155348</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30839,28 +30979,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2506822652134473</v>
+        <v>0.2520590878196949</v>
       </c>
       <c r="J11" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K11" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1577462019045364</v>
+        <v>0.1606347641172094</v>
       </c>
       <c r="M11" t="n">
-        <v>3.505675281369164</v>
+        <v>3.495979491658014</v>
       </c>
       <c r="N11" t="n">
-        <v>18.62244597774485</v>
+        <v>18.54280746686209</v>
       </c>
       <c r="O11" t="n">
-        <v>4.315373214189573</v>
+        <v>4.306136025122997</v>
       </c>
       <c r="P11" t="n">
-        <v>367.6683335411437</v>
+        <v>367.6538343840168</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30917,28 +31057,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2337312581612748</v>
+        <v>0.2353584779778247</v>
       </c>
       <c r="J12" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K12" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1064001962500282</v>
+        <v>0.1087514074047123</v>
       </c>
       <c r="M12" t="n">
-        <v>4.258608847481202</v>
+        <v>4.245164364106162</v>
       </c>
       <c r="N12" t="n">
-        <v>25.46476455313632</v>
+        <v>25.35613148209795</v>
       </c>
       <c r="O12" t="n">
-        <v>5.046262434033363</v>
+        <v>5.035487213974229</v>
       </c>
       <c r="P12" t="n">
-        <v>362.7493347451561</v>
+        <v>362.7321990396895</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30995,28 +31135,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2476335917338069</v>
+        <v>0.2489961691363766</v>
       </c>
       <c r="J13" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K13" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1114845890975892</v>
+        <v>0.1136584656885394</v>
       </c>
       <c r="M13" t="n">
-        <v>4.401013585990492</v>
+        <v>4.385929194189431</v>
       </c>
       <c r="N13" t="n">
-        <v>27.1253078999474</v>
+        <v>27.00498703621196</v>
       </c>
       <c r="O13" t="n">
-        <v>5.208196223256897</v>
+        <v>5.196632278332956</v>
       </c>
       <c r="P13" t="n">
-        <v>358.0893480418268</v>
+        <v>358.0749981508275</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31073,28 +31213,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.187213351236221</v>
+        <v>0.1896406296296897</v>
       </c>
       <c r="J14" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K14" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05996167605728742</v>
+        <v>0.0620166485205742</v>
       </c>
       <c r="M14" t="n">
-        <v>4.716973805575487</v>
+        <v>4.704476598612682</v>
       </c>
       <c r="N14" t="n">
-        <v>30.7351861029342</v>
+        <v>30.61830027928904</v>
       </c>
       <c r="O14" t="n">
-        <v>5.543932368178223</v>
+        <v>5.533380547123886</v>
       </c>
       <c r="P14" t="n">
-        <v>352.2294201875931</v>
+        <v>352.2040021694073</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31151,28 +31291,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2898987556520325</v>
+        <v>0.2915615056171453</v>
       </c>
       <c r="J15" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K15" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L15" t="n">
-        <v>0.108398012136518</v>
+        <v>0.110559596186056</v>
       </c>
       <c r="M15" t="n">
-        <v>5.284913545994861</v>
+        <v>5.265856626499526</v>
       </c>
       <c r="N15" t="n">
-        <v>38.66631895288413</v>
+        <v>38.49570183865301</v>
       </c>
       <c r="O15" t="n">
-        <v>6.218224742873494</v>
+        <v>6.204490457616404</v>
       </c>
       <c r="P15" t="n">
-        <v>350.0772527056853</v>
+        <v>350.0598411289049</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31229,28 +31369,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2753185662958993</v>
+        <v>0.2780107555034688</v>
       </c>
       <c r="J16" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K16" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07732996747544751</v>
+        <v>0.07948508338023641</v>
       </c>
       <c r="M16" t="n">
-        <v>5.852903658468092</v>
+        <v>5.835489821459861</v>
       </c>
       <c r="N16" t="n">
-        <v>50.58945525509822</v>
+        <v>50.38483673080453</v>
       </c>
       <c r="O16" t="n">
-        <v>7.112626466720871</v>
+        <v>7.09822771759293</v>
       </c>
       <c r="P16" t="n">
-        <v>352.7404566435043</v>
+        <v>352.7122641206669</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31307,28 +31447,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2192970888448019</v>
+        <v>0.2214561842381417</v>
       </c>
       <c r="J17" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K17" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03903838030887319</v>
+        <v>0.04019237075512305</v>
       </c>
       <c r="M17" t="n">
-        <v>6.714523288856832</v>
+        <v>6.690543570850153</v>
       </c>
       <c r="N17" t="n">
-        <v>66.21713729266121</v>
+        <v>65.92462413482194</v>
       </c>
       <c r="O17" t="n">
-        <v>8.137391307578936</v>
+        <v>8.11939801554413</v>
       </c>
       <c r="P17" t="n">
-        <v>352.3949925978698</v>
+        <v>352.3723831025755</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31366,7 +31506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R418"/>
+  <dimension ref="A1:R420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69769,6 +69909,190 @@
         </is>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-36.83572752731763,175.8022485902644</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-36.8360965323054,175.8030194450315</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-36.83641217034934,175.80383144882458</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-36.836819682568056,175.80457260738723</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-36.83718112094716,175.80535179180174</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-36.83758433996563,175.80609874788067</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-36.83800400277764,175.80682945109274</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-36.83839841415721,175.8075772933353</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-36.83879104896422,175.80832391452284</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-36.83916883755437,175.80908568307996</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-36.83958844207273,175.80981976163005</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-36.84001418532457,175.81054801952183</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-36.84045113677477,175.81126655647722</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-36.84088554523082,175.81198020286146</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-36.84132249369457,175.81269251049346</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-36.84177188534688,175.81339380184022</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-36.835704022430626,175.8022667149598</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-36.836079382109496,175.8030326695061</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-36.83639961391612,175.80384113097273</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-36.836812102748944,175.80457845207823</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-36.83717626268301,175.80535565288173</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-36.837578414336015,175.80610364999026</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-36.83800183439676,175.80683126335984</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-36.83839773477575,175.80757784365917</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-36.83878613672432,175.80832766846692</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-36.8391680644533,175.80908625821485</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-36.839588750030785,175.80981952892776</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-36.84001096549901,175.8105504908193</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-36.84044889450782,175.81126843291912</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-36.84088540212402,175.81198033901455</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-36.841318840329215,175.8126959756644</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-36.84177042810942,175.8133951197167</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R420"/>
+  <dimension ref="A1:R421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25635,6 +25635,66 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>364.38</v>
+      </c>
+      <c r="C421" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="D421" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="E421" t="n">
+        <v>372.75</v>
+      </c>
+      <c r="F421" t="n">
+        <v>375.99</v>
+      </c>
+      <c r="G421" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="H421" t="n">
+        <v>374.37</v>
+      </c>
+      <c r="I421" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="J421" t="n">
+        <v>376.93</v>
+      </c>
+      <c r="K421" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="L421" t="n">
+        <v>371.47</v>
+      </c>
+      <c r="M421" t="n">
+        <v>367.29</v>
+      </c>
+      <c r="N421" t="n">
+        <v>360.59</v>
+      </c>
+      <c r="O421" t="n">
+        <v>360.41</v>
+      </c>
+      <c r="P421" t="n">
+        <v>363.79</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25646,7 +25706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B446"/>
+  <dimension ref="A1:B447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30109,6 +30169,16 @@
       </c>
       <c r="B446" t="n">
         <v>-0.85</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -30277,28 +30347,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.325349342329661</v>
+        <v>0.3252753869010972</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1581102291364387</v>
+        <v>0.1587896744118771</v>
       </c>
       <c r="M2" t="n">
-        <v>4.314689932090038</v>
+        <v>4.30476478758624</v>
       </c>
       <c r="N2" t="n">
-        <v>31.53995095511464</v>
+        <v>31.46455167510108</v>
       </c>
       <c r="O2" t="n">
-        <v>5.616044066343732</v>
+        <v>5.609327203426547</v>
       </c>
       <c r="P2" t="n">
-        <v>355.78875298422</v>
+        <v>355.7895339187345</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30355,28 +30425,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4995437531678678</v>
+        <v>0.4977843035714401</v>
       </c>
       <c r="J3" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K3" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3142728809026293</v>
+        <v>0.3137276609385597</v>
       </c>
       <c r="M3" t="n">
-        <v>4.327507313666987</v>
+        <v>4.32665259882988</v>
       </c>
       <c r="N3" t="n">
-        <v>30.46894143723305</v>
+        <v>30.4272628548583</v>
       </c>
       <c r="O3" t="n">
-        <v>5.519867882226263</v>
+        <v>5.516091266001524</v>
       </c>
       <c r="P3" t="n">
-        <v>356.6543750872869</v>
+        <v>356.6729540468451</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30433,28 +30503,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3251456629799145</v>
+        <v>0.3241289996076903</v>
       </c>
       <c r="J4" t="n">
+        <v>420</v>
+      </c>
+      <c r="K4" t="n">
         <v>419</v>
       </c>
-      <c r="K4" t="n">
-        <v>418</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2143288884847407</v>
+        <v>0.2141290124908014</v>
       </c>
       <c r="M4" t="n">
-        <v>3.517129812127255</v>
+        <v>3.513234526097221</v>
       </c>
       <c r="N4" t="n">
-        <v>21.64588437986004</v>
+        <v>21.60461625912975</v>
       </c>
       <c r="O4" t="n">
-        <v>4.652513769980702</v>
+        <v>4.64807661932651</v>
       </c>
       <c r="P4" t="n">
-        <v>368.3768555057576</v>
+        <v>368.3875953114378</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30511,28 +30581,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3937257967489245</v>
+        <v>0.3909814807721089</v>
       </c>
       <c r="J5" t="n">
+        <v>420</v>
+      </c>
+      <c r="K5" t="n">
         <v>419</v>
       </c>
-      <c r="K5" t="n">
-        <v>418</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2485863528050958</v>
+        <v>0.2464764319772959</v>
       </c>
       <c r="M5" t="n">
-        <v>3.767243464430002</v>
+        <v>3.769417948153309</v>
       </c>
       <c r="N5" t="n">
-        <v>26.17272049906289</v>
+        <v>26.18598130092411</v>
       </c>
       <c r="O5" t="n">
-        <v>5.115928117073469</v>
+        <v>5.117223983853365</v>
       </c>
       <c r="P5" t="n">
-        <v>367.82299572264</v>
+        <v>367.8519860660724</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30589,28 +30659,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3965448448119375</v>
+        <v>0.3954553290934871</v>
       </c>
       <c r="J6" t="n">
+        <v>420</v>
+      </c>
+      <c r="K6" t="n">
         <v>419</v>
       </c>
-      <c r="K6" t="n">
-        <v>418</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3289252129633994</v>
+        <v>0.3287899433592184</v>
       </c>
       <c r="M6" t="n">
-        <v>3.205527233180833</v>
+        <v>3.202651892168344</v>
       </c>
       <c r="N6" t="n">
-        <v>17.91916236706248</v>
+        <v>17.88833138265105</v>
       </c>
       <c r="O6" t="n">
-        <v>4.233103160455989</v>
+        <v>4.229459939832868</v>
       </c>
       <c r="P6" t="n">
-        <v>367.5791493363543</v>
+        <v>367.590658738012</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30667,28 +30737,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4444067609439727</v>
+        <v>0.4433927758752596</v>
       </c>
       <c r="J7" t="n">
+        <v>420</v>
+      </c>
+      <c r="K7" t="n">
         <v>419</v>
       </c>
-      <c r="K7" t="n">
-        <v>418</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3676664563306185</v>
+        <v>0.3677693550177329</v>
       </c>
       <c r="M7" t="n">
-        <v>3.136965099100494</v>
+        <v>3.134016542612866</v>
       </c>
       <c r="N7" t="n">
-        <v>18.97198866755483</v>
+        <v>18.93704747445246</v>
       </c>
       <c r="O7" t="n">
-        <v>4.355684638211866</v>
+        <v>4.351671802244795</v>
       </c>
       <c r="P7" t="n">
-        <v>366.3498612307386</v>
+        <v>366.3605727434162</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30745,28 +30815,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3932789722815787</v>
+        <v>0.3927877157159073</v>
       </c>
       <c r="J8" t="n">
+        <v>420</v>
+      </c>
+      <c r="K8" t="n">
         <v>419</v>
       </c>
-      <c r="K8" t="n">
-        <v>418</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3392417568218102</v>
+        <v>0.3398949868406913</v>
       </c>
       <c r="M8" t="n">
-        <v>3.256667681362513</v>
+        <v>3.251144472451431</v>
       </c>
       <c r="N8" t="n">
-        <v>16.82651082222305</v>
+        <v>16.78877864398612</v>
       </c>
       <c r="O8" t="n">
-        <v>4.102013020728121</v>
+        <v>4.097411212459169</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8130723393589</v>
+        <v>364.8182618644255</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30823,28 +30893,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3349558468425779</v>
+        <v>0.3354534706441815</v>
       </c>
       <c r="J9" t="n">
+        <v>420</v>
+      </c>
+      <c r="K9" t="n">
         <v>419</v>
       </c>
-      <c r="K9" t="n">
-        <v>418</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.2225712293626437</v>
+        <v>0.2240302213886664</v>
       </c>
       <c r="M9" t="n">
-        <v>3.657658819240203</v>
+        <v>3.651512179934751</v>
       </c>
       <c r="N9" t="n">
-        <v>21.88900601276285</v>
+        <v>21.8392548165875</v>
       </c>
       <c r="O9" t="n">
-        <v>4.67856879961841</v>
+        <v>4.673248850274025</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2690463411745</v>
+        <v>366.2637895540441</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30901,28 +30971,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2816725820371285</v>
+        <v>0.2824234755757514</v>
       </c>
       <c r="J10" t="n">
+        <v>420</v>
+      </c>
+      <c r="K10" t="n">
         <v>419</v>
       </c>
-      <c r="K10" t="n">
-        <v>418</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.2057146676989033</v>
+        <v>0.2074437964452986</v>
       </c>
       <c r="M10" t="n">
-        <v>3.31108431958543</v>
+        <v>3.306875782602126</v>
       </c>
       <c r="N10" t="n">
-        <v>17.11038431638048</v>
+        <v>17.07521739499121</v>
       </c>
       <c r="O10" t="n">
-        <v>4.136470030881462</v>
+        <v>4.132217007248192</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8172834155348</v>
+        <v>367.8093511432492</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30979,28 +31049,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2520590878196949</v>
+        <v>0.2531272726663069</v>
       </c>
       <c r="J11" t="n">
+        <v>420</v>
+      </c>
+      <c r="K11" t="n">
         <v>419</v>
       </c>
-      <c r="K11" t="n">
-        <v>418</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1606347641172094</v>
+        <v>0.162449038882058</v>
       </c>
       <c r="M11" t="n">
-        <v>3.495979491658014</v>
+        <v>3.493113183390735</v>
       </c>
       <c r="N11" t="n">
-        <v>18.54280746686209</v>
+        <v>18.51002529008602</v>
       </c>
       <c r="O11" t="n">
-        <v>4.306136025122997</v>
+        <v>4.30232789197732</v>
       </c>
       <c r="P11" t="n">
-        <v>367.6538343840168</v>
+        <v>367.6425503169435</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31057,28 +31127,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2353584779778247</v>
+        <v>0.2365287919957952</v>
       </c>
       <c r="J12" t="n">
+        <v>420</v>
+      </c>
+      <c r="K12" t="n">
         <v>419</v>
       </c>
-      <c r="K12" t="n">
-        <v>418</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1087514074047123</v>
+        <v>0.1102072802926082</v>
       </c>
       <c r="M12" t="n">
-        <v>4.245164364106162</v>
+        <v>4.239969489988082</v>
       </c>
       <c r="N12" t="n">
-        <v>25.35613148209795</v>
+        <v>25.30938708075324</v>
       </c>
       <c r="O12" t="n">
-        <v>5.035487213974229</v>
+        <v>5.030843575460604</v>
       </c>
       <c r="P12" t="n">
-        <v>362.7321990396895</v>
+        <v>362.7198361027715</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31135,28 +31205,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2489961691363766</v>
+        <v>0.2502184334010462</v>
       </c>
       <c r="J13" t="n">
+        <v>420</v>
+      </c>
+      <c r="K13" t="n">
         <v>419</v>
       </c>
-      <c r="K13" t="n">
-        <v>418</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1136584656885394</v>
+        <v>0.1151572821519905</v>
       </c>
       <c r="M13" t="n">
-        <v>4.385929194189431</v>
+        <v>4.380768867185832</v>
       </c>
       <c r="N13" t="n">
-        <v>27.00498703621196</v>
+        <v>26.95555718230358</v>
       </c>
       <c r="O13" t="n">
-        <v>5.196632278332956</v>
+        <v>5.191874149312903</v>
       </c>
       <c r="P13" t="n">
-        <v>358.0749981508275</v>
+        <v>358.062086423061</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31213,28 +31283,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1896406296296897</v>
+        <v>0.1912263484362164</v>
       </c>
       <c r="J14" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K14" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0620166485205742</v>
+        <v>0.06327048403539925</v>
       </c>
       <c r="M14" t="n">
-        <v>4.704476598612682</v>
+        <v>4.699795879275379</v>
       </c>
       <c r="N14" t="n">
-        <v>30.61830027928904</v>
+        <v>30.57097356575152</v>
       </c>
       <c r="O14" t="n">
-        <v>5.533380547123886</v>
+        <v>5.529102419538954</v>
       </c>
       <c r="P14" t="n">
-        <v>352.2040021694073</v>
+        <v>352.1873447682688</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31291,28 +31361,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2915615056171453</v>
+        <v>0.2927720083375441</v>
       </c>
       <c r="J15" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K15" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L15" t="n">
-        <v>0.110559596186056</v>
+        <v>0.1118876827954632</v>
       </c>
       <c r="M15" t="n">
-        <v>5.265856626499526</v>
+        <v>5.257762009692243</v>
       </c>
       <c r="N15" t="n">
-        <v>38.49570183865301</v>
+        <v>38.41894854876875</v>
       </c>
       <c r="O15" t="n">
-        <v>6.204490457616404</v>
+        <v>6.198302069822732</v>
       </c>
       <c r="P15" t="n">
-        <v>350.0598411289049</v>
+        <v>350.0471252367116</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31369,28 +31439,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2780107555034688</v>
+        <v>0.2797509081601738</v>
       </c>
       <c r="J16" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K16" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07948508338023641</v>
+        <v>0.0807678237514351</v>
       </c>
       <c r="M16" t="n">
-        <v>5.835489821459861</v>
+        <v>5.828327101664267</v>
       </c>
       <c r="N16" t="n">
-        <v>50.38483673080453</v>
+        <v>50.29567072845526</v>
       </c>
       <c r="O16" t="n">
-        <v>7.09822771759293</v>
+        <v>7.091944072569612</v>
       </c>
       <c r="P16" t="n">
-        <v>352.7122641206669</v>
+        <v>352.6939844479244</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31447,28 +31517,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2214561842381417</v>
+        <v>0.2229745394039962</v>
       </c>
       <c r="J17" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K17" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04019237075512305</v>
+        <v>0.04092572211503487</v>
       </c>
       <c r="M17" t="n">
-        <v>6.690543570850153</v>
+        <v>6.680229772747362</v>
       </c>
       <c r="N17" t="n">
-        <v>65.92462413482194</v>
+        <v>65.79110805663815</v>
       </c>
       <c r="O17" t="n">
-        <v>8.11939801554413</v>
+        <v>8.111171805395207</v>
       </c>
       <c r="P17" t="n">
-        <v>352.3723831025755</v>
+        <v>352.3564333320587</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31506,7 +31576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R420"/>
+  <dimension ref="A1:R421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70093,6 +70163,98 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-36.835692231704655,175.8022758068225</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-36.83606636633497,175.80304270593385</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-36.83639073253612,175.80384797931958</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-36.83679809156752,175.804589255898</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-36.837164268842926,175.80536518492096</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-36.83757031347498,175.80611035160726</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-36.837996226515074,175.80683595025704</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-36.83839252618443,175.80758206280868</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-36.83878030343933,175.8083321262749</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-36.83916203426474,175.80909074426674</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-36.83958259086978,175.80982418297276</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-36.840003682560095,175.81055608065813</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-36.840443812035936,175.81127268618704</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-36.84087946319123,175.81198598936797</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-36.84131432734835,175.81270025616925</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-36.84176416198819,175.81340078658496</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0180/nzd0180.xlsx
+++ b/data/nzd0180/nzd0180.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R421"/>
+  <dimension ref="A1:R422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25695,6 +25695,66 @@
         </is>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="C422" t="n">
+        <v>366.98</v>
+      </c>
+      <c r="D422" t="n">
+        <v>376.06</v>
+      </c>
+      <c r="E422" t="n">
+        <v>376.38</v>
+      </c>
+      <c r="F422" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="G422" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="H422" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="I422" t="n">
+        <v>376.36</v>
+      </c>
+      <c r="J422" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="K422" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="L422" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="M422" t="n">
+        <v>367.25</v>
+      </c>
+      <c r="N422" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="O422" t="n">
+        <v>359.52</v>
+      </c>
+      <c r="P422" t="n">
+        <v>361.58</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25706,7 +25766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B447"/>
+  <dimension ref="A1:B448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30179,6 +30239,16 @@
       </c>
       <c r="B447" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -30347,28 +30417,28 @@
         <v>0.1264</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3252753869010972</v>
+        <v>0.3246439872931737</v>
       </c>
       <c r="J2" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1587896744118771</v>
+        <v>0.1590018432736829</v>
       </c>
       <c r="M2" t="n">
-        <v>4.30476478758624</v>
+        <v>4.297844291871093</v>
       </c>
       <c r="N2" t="n">
-        <v>31.46455167510108</v>
+        <v>31.39345458406751</v>
       </c>
       <c r="O2" t="n">
-        <v>5.609327203426547</v>
+        <v>5.602986220228238</v>
       </c>
       <c r="P2" t="n">
-        <v>355.7895339187345</v>
+        <v>355.796230866437</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30425,28 +30495,28 @@
         <v>0.1171</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4977843035714401</v>
+        <v>0.4962668272951914</v>
       </c>
       <c r="J3" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3137276609385597</v>
+        <v>0.3134552156954468</v>
       </c>
       <c r="M3" t="n">
-        <v>4.32665259882988</v>
+        <v>4.324428373175103</v>
       </c>
       <c r="N3" t="n">
-        <v>30.4272628548583</v>
+        <v>30.37773294552372</v>
       </c>
       <c r="O3" t="n">
-        <v>5.516091266001524</v>
+        <v>5.511599853538328</v>
       </c>
       <c r="P3" t="n">
-        <v>356.6729540468451</v>
+        <v>356.6890491776218</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30503,28 +30573,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3241289996076903</v>
+        <v>0.3236082278538333</v>
       </c>
       <c r="J4" t="n">
+        <v>421</v>
+      </c>
+      <c r="K4" t="n">
         <v>420</v>
       </c>
-      <c r="K4" t="n">
-        <v>419</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2141290124908014</v>
+        <v>0.2145103098421536</v>
       </c>
       <c r="M4" t="n">
-        <v>3.513234526097221</v>
+        <v>3.507159376745809</v>
       </c>
       <c r="N4" t="n">
-        <v>21.60461625912975</v>
+        <v>21.55588841963815</v>
       </c>
       <c r="O4" t="n">
-        <v>4.64807661932651</v>
+        <v>4.642831939628889</v>
       </c>
       <c r="P4" t="n">
-        <v>368.3875953114378</v>
+        <v>368.3931210142779</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30581,28 +30651,28 @@
         <v>0.1596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3909814807721089</v>
+        <v>0.3900009928057979</v>
       </c>
       <c r="J5" t="n">
+        <v>421</v>
+      </c>
+      <c r="K5" t="n">
         <v>420</v>
       </c>
-      <c r="K5" t="n">
-        <v>419</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2464764319772959</v>
+        <v>0.246516635258123</v>
       </c>
       <c r="M5" t="n">
-        <v>3.769417948153309</v>
+        <v>3.764508134095229</v>
       </c>
       <c r="N5" t="n">
-        <v>26.18598130092411</v>
+        <v>26.13324619699237</v>
       </c>
       <c r="O5" t="n">
-        <v>5.117223983853365</v>
+        <v>5.112068680778102</v>
       </c>
       <c r="P5" t="n">
-        <v>367.8519860660724</v>
+        <v>367.8623896355823</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30659,28 +30729,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3954553290934871</v>
+        <v>0.3946075784154905</v>
       </c>
       <c r="J6" t="n">
+        <v>421</v>
+      </c>
+      <c r="K6" t="n">
         <v>420</v>
       </c>
-      <c r="K6" t="n">
-        <v>419</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3287899433592184</v>
+        <v>0.3289911327153414</v>
       </c>
       <c r="M6" t="n">
-        <v>3.202651892168344</v>
+        <v>3.198721952298901</v>
       </c>
       <c r="N6" t="n">
-        <v>17.88833138265105</v>
+        <v>17.85292611029308</v>
       </c>
       <c r="O6" t="n">
-        <v>4.229459939832868</v>
+        <v>4.225272311969144</v>
       </c>
       <c r="P6" t="n">
-        <v>367.590658738012</v>
+        <v>367.5996538847233</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30737,28 +30807,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4433927758752596</v>
+        <v>0.4424801542714593</v>
       </c>
       <c r="J7" t="n">
+        <v>421</v>
+      </c>
+      <c r="K7" t="n">
         <v>420</v>
       </c>
-      <c r="K7" t="n">
-        <v>419</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3677693550177329</v>
+        <v>0.3680122902539866</v>
       </c>
       <c r="M7" t="n">
-        <v>3.134016542612866</v>
+        <v>3.130587519659418</v>
       </c>
       <c r="N7" t="n">
-        <v>18.93704747445246</v>
+        <v>18.90028709863341</v>
       </c>
       <c r="O7" t="n">
-        <v>4.351671802244795</v>
+        <v>4.34744604321128</v>
       </c>
       <c r="P7" t="n">
-        <v>366.3605727434162</v>
+        <v>366.3702562098306</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30815,28 +30885,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3927877157159073</v>
+        <v>0.3920071008901983</v>
       </c>
       <c r="J8" t="n">
+        <v>421</v>
+      </c>
+      <c r="K8" t="n">
         <v>420</v>
       </c>
-      <c r="K8" t="n">
-        <v>419</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.3398949868406913</v>
+        <v>0.3401785885779024</v>
       </c>
       <c r="M8" t="n">
-        <v>3.251144472451431</v>
+        <v>3.24693358294748</v>
       </c>
       <c r="N8" t="n">
-        <v>16.78877864398612</v>
+        <v>16.75489826190447</v>
       </c>
       <c r="O8" t="n">
-        <v>4.097411212459169</v>
+        <v>4.093274760128431</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8182618644255</v>
+        <v>364.8265446591958</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30893,28 +30963,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3354534706441815</v>
+        <v>0.3359622237959457</v>
       </c>
       <c r="J9" t="n">
+        <v>421</v>
+      </c>
+      <c r="K9" t="n">
         <v>420</v>
       </c>
-      <c r="K9" t="n">
-        <v>419</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.2240302213886664</v>
+        <v>0.22551453193987</v>
       </c>
       <c r="M9" t="n">
-        <v>3.651512179934751</v>
+        <v>3.645427367380657</v>
       </c>
       <c r="N9" t="n">
-        <v>21.8392548165875</v>
+        <v>21.78984459346748</v>
       </c>
       <c r="O9" t="n">
-        <v>4.673248850274025</v>
+        <v>4.667959360734354</v>
       </c>
       <c r="P9" t="n">
-        <v>366.2637895540441</v>
+        <v>366.2583913758313</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30971,28 +31041,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2824234755757514</v>
+        <v>0.2832368073899584</v>
       </c>
       <c r="J10" t="n">
+        <v>421</v>
+      </c>
+      <c r="K10" t="n">
         <v>420</v>
       </c>
-      <c r="K10" t="n">
-        <v>419</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.2074437964452986</v>
+        <v>0.2092530628863201</v>
       </c>
       <c r="M10" t="n">
-        <v>3.306875782602126</v>
+        <v>3.302955798642166</v>
       </c>
       <c r="N10" t="n">
-        <v>17.07521739499121</v>
+        <v>17.04117644777329</v>
       </c>
       <c r="O10" t="n">
-        <v>4.132217007248192</v>
+        <v>4.128095983352772</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8093511432492</v>
+        <v>367.8007212014707</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31049,28 +31119,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2531272726663069</v>
+        <v>0.2545298394464945</v>
       </c>
       <c r="J11" t="n">
+        <v>421</v>
+      </c>
+      <c r="K11" t="n">
         <v>420</v>
       </c>
-      <c r="K11" t="n">
-        <v>419</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.162449038882058</v>
+        <v>0.1645817765495542</v>
       </c>
       <c r="M11" t="n">
-        <v>3.493113183390735</v>
+        <v>3.491904745194152</v>
       </c>
       <c r="N11" t="n">
-        <v>18.51002529008602</v>
+        <v>18.48562349446931</v>
       </c>
       <c r="O11" t="n">
-        <v>4.30232789197732</v>
+        <v>4.299491073891107</v>
       </c>
       <c r="P11" t="n">
-        <v>367.6425503169435</v>
+        <v>367.6276682362945</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31127,28 +31197,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2365287919957952</v>
+        <v>0.2377184095111226</v>
       </c>
       <c r="J12" t="n">
+        <v>421</v>
+      </c>
+      <c r="K12" t="n">
         <v>420</v>
       </c>
-      <c r="K12" t="n">
-        <v>419</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1102072802926082</v>
+        <v>0.1116947306338997</v>
       </c>
       <c r="M12" t="n">
-        <v>4.239969489988082</v>
+        <v>4.234828065824765</v>
       </c>
       <c r="N12" t="n">
-        <v>25.30938708075324</v>
+        <v>25.2632769203637</v>
       </c>
       <c r="O12" t="n">
-        <v>5.030843575460604</v>
+        <v>5.026258739894287</v>
       </c>
       <c r="P12" t="n">
-        <v>362.7198361027715</v>
+        <v>362.7072135424381</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31205,28 +31275,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2502184334010462</v>
+        <v>0.2514048163097796</v>
       </c>
       <c r="J13" t="n">
+        <v>421</v>
+      </c>
+      <c r="K13" t="n">
         <v>420</v>
       </c>
-      <c r="K13" t="n">
-        <v>419</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.1151572821519905</v>
+        <v>0.1166475046972532</v>
       </c>
       <c r="M13" t="n">
-        <v>4.380768867185832</v>
+        <v>4.375424507818567</v>
       </c>
       <c r="N13" t="n">
-        <v>26.95555718230358</v>
+        <v>26.90545072378614</v>
       </c>
       <c r="O13" t="n">
-        <v>5.191874149312903</v>
+        <v>5.18704643547618</v>
       </c>
       <c r="P13" t="n">
-        <v>358.062086423061</v>
+        <v>358.0494981838572</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31283,28 +31353,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1912263484362164</v>
+        <v>0.1924487783061294</v>
       </c>
       <c r="J14" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K14" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06327048403539925</v>
+        <v>0.06433574952093357</v>
       </c>
       <c r="M14" t="n">
-        <v>4.699795879275379</v>
+        <v>4.693593632934834</v>
       </c>
       <c r="N14" t="n">
-        <v>30.57097356575152</v>
+        <v>30.5134723395565</v>
       </c>
       <c r="O14" t="n">
-        <v>5.529102419538954</v>
+        <v>5.523900102242663</v>
       </c>
       <c r="P14" t="n">
-        <v>352.1873447682688</v>
+        <v>352.1744462680395</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31361,28 +31431,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2927720083375441</v>
+        <v>0.2935317036543074</v>
       </c>
       <c r="J15" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K15" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1118876827954632</v>
+        <v>0.1129469390982081</v>
       </c>
       <c r="M15" t="n">
-        <v>5.257762009692243</v>
+        <v>5.248021757467295</v>
       </c>
       <c r="N15" t="n">
-        <v>38.41894854876875</v>
+        <v>38.33352938371843</v>
       </c>
       <c r="O15" t="n">
-        <v>6.198302069822732</v>
+        <v>6.191407706145544</v>
       </c>
       <c r="P15" t="n">
-        <v>350.0471252367116</v>
+        <v>350.0391092920274</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31439,28 +31509,28 @@
         <v>0.1681</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2797509081601738</v>
+        <v>0.2803975368103173</v>
       </c>
       <c r="J16" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K16" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0807678237514351</v>
+        <v>0.08152226953253261</v>
       </c>
       <c r="M16" t="n">
-        <v>5.828327101664267</v>
+        <v>5.816949363629249</v>
       </c>
       <c r="N16" t="n">
-        <v>50.29567072845526</v>
+        <v>50.18043258886149</v>
       </c>
       <c r="O16" t="n">
-        <v>7.091944072569612</v>
+        <v>7.083814833044515</v>
       </c>
       <c r="P16" t="n">
-        <v>352.6939844479244</v>
+        <v>352.6871615290826</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31517,28 +31587,28 @@
         <v>0.1312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2229745394039962</v>
+        <v>0.2237151081547771</v>
       </c>
       <c r="J17" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K17" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04092572211503487</v>
+        <v>0.04140459283994824</v>
       </c>
       <c r="M17" t="n">
-        <v>6.680229772747362</v>
+        <v>6.667063103683891</v>
       </c>
       <c r="N17" t="n">
-        <v>65.79110805663815</v>
+        <v>65.64038166136612</v>
       </c>
       <c r="O17" t="n">
-        <v>8.111171805395207</v>
+        <v>8.101875194136609</v>
       </c>
       <c r="P17" t="n">
-        <v>352.3564333320587</v>
+        <v>352.3486192018277</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31576,7 +31646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R421"/>
+  <dimension ref="A1:R422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70255,6 +70325,98 @@
         </is>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-36.835700730214995,175.8022692535971</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-36.836062308475704,175.80304583493714</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-36.83638276991927,175.8038541192154</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-36.836770298893626,175.80461068641435</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-36.83716024559263,175.80536838237649</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-36.83756843827562,175.80611190290728</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-36.838000413733404,175.8068324507072</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-36.83839207326344,175.80758242969122</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-36.83877899862554,175.80833312341608</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-36.83915639062661,175.80909494275056</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-36.83958197495368,175.8098246483772</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-36.84000398921015,175.81055584529653</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-36.840449118734504,175.81126824527493</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-36.84088583144445,175.81197993055522</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-36.841330158598055,175.8126852404279</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-36.8417755284405,175.8133905071488</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
